--- a/artfynd/A 8644-2022 artfynd.xlsx
+++ b/artfynd/A 8644-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8644-2022 artfynd.xlsx
+++ b/artfynd/A 8644-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113024380</v>
       </c>
       <c r="B2" t="n">
-        <v>90241</v>
+        <v>90763</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,6 +709,9 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grävstaviken, Upl</t>
@@ -773,14 +776,18 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>113024392</v>
       </c>
       <c r="B3" t="n">
-        <v>90593</v>
+        <v>91116</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,6 +818,9 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grävstaviken, Upl</t>
@@ -875,14 +885,18 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>113024377</v>
       </c>
       <c r="B4" t="n">
-        <v>89586</v>
+        <v>90089</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,6 +927,9 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grävstaviken, Upl</t>
@@ -977,14 +994,18 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>113024399</v>
       </c>
       <c r="B5" t="n">
-        <v>90661</v>
+        <v>91185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,13 +1036,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grävstaviken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707572</v>
+        <v>707571</v>
       </c>
       <c r="R5" t="n">
         <v>6633955</v>
@@ -1079,7 +1103,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1290,7 +1318,7 @@
         <v>113024382</v>
       </c>
       <c r="B8" t="n">
-        <v>89586</v>
+        <v>90089</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,6 +1349,9 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Grävstaviken, Upl</t>
@@ -1330,7 +1361,7 @@
         <v>707577</v>
       </c>
       <c r="R8" t="n">
-        <v>6634086</v>
+        <v>6634085</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1385,14 +1416,18 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>113024383</v>
       </c>
       <c r="B9" t="n">
-        <v>86848</v>
+        <v>87392</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,6 +1458,9 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Grävstaviken, Upl</t>
@@ -1487,7 +1525,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8644-2022 artfynd.xlsx
+++ b/artfynd/A 8644-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113024380</v>
       </c>
       <c r="B2" t="n">
-        <v>90763</v>
+        <v>90781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>113024392</v>
       </c>
       <c r="B3" t="n">
-        <v>91116</v>
+        <v>91134</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>113024377</v>
       </c>
       <c r="B4" t="n">
-        <v>90089</v>
+        <v>90106</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>113024399</v>
       </c>
       <c r="B5" t="n">
-        <v>91185</v>
+        <v>91203</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>113024382</v>
       </c>
       <c r="B8" t="n">
-        <v>90089</v>
+        <v>90106</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>113024383</v>
       </c>
       <c r="B9" t="n">
-        <v>87392</v>
+        <v>87409</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
